--- a/backend/config/playernumber.xlsx
+++ b/backend/config/playernumber.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="B服" sheetId="1" r:id="rId1"/>
     <sheet name="渠道" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">B服!$A$1:$F$226</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">B服!$A$1:$F$230</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -1096,7 +1096,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G226"/>
+  <dimension ref="A1:G230"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -5800,8 +5800,8 @@
       <c r="D226" s="8">
         <v>170899</v>
       </c>
-      <c r="E226" s="2" t="s">
-        <v>10</v>
+      <c r="E226" s="2">
+        <v>2</v>
       </c>
       <c r="F226" s="2" t="s">
         <v>9</v>
@@ -5810,9 +5810,101 @@
         <v>15</v>
       </c>
     </row>
+    <row r="227" spans="1:7">
+      <c r="A227" s="2">
+        <v>298</v>
+      </c>
+      <c r="B227" s="7">
+        <v>46042</v>
+      </c>
+      <c r="C227" s="7">
+        <v>46051</v>
+      </c>
+      <c r="D227" s="8">
+        <v>141207</v>
+      </c>
+      <c r="E227" s="2">
+        <v>3</v>
+      </c>
+      <c r="F227" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G227" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7">
+      <c r="A228" s="2">
+        <v>300</v>
+      </c>
+      <c r="B228" s="7">
+        <v>46053</v>
+      </c>
+      <c r="C228" s="7">
+        <v>46062</v>
+      </c>
+      <c r="D228" s="8">
+        <v>137065</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F228" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G228" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7">
+      <c r="A229" s="2">
+        <v>299</v>
+      </c>
+      <c r="B229" s="7">
+        <v>46064</v>
+      </c>
+      <c r="C229" s="7">
+        <v>46073</v>
+      </c>
+      <c r="D229" s="8">
+        <v>159812</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F229" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G229" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7">
+      <c r="A230" s="2">
+        <v>301</v>
+      </c>
+      <c r="B230" s="7">
+        <v>46075</v>
+      </c>
+      <c r="C230" s="7">
+        <v>46084</v>
+      </c>
+      <c r="D230" s="8">
+        <v>144103</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F230" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G230" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F226" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F230" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:G193">
@@ -9757,20 +9849,88 @@
       </c>
     </row>
     <row r="188" spans="1:6">
-      <c r="A188" s="2"/>
-      <c r="F188" s="2"/>
+      <c r="A188" s="2">
+        <v>298</v>
+      </c>
+      <c r="B188" s="7">
+        <v>46042</v>
+      </c>
+      <c r="C188" s="7">
+        <v>46051</v>
+      </c>
+      <c r="D188" s="3">
+        <v>45976</v>
+      </c>
+      <c r="E188" s="5">
+        <f>D188/B服!D227</f>
+        <v>0.325592923863548</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="189" spans="1:6">
-      <c r="A189" s="2"/>
-      <c r="F189" s="2"/>
+      <c r="A189" s="2">
+        <v>300</v>
+      </c>
+      <c r="B189" s="7">
+        <v>46053</v>
+      </c>
+      <c r="C189" s="7">
+        <v>46062</v>
+      </c>
+      <c r="D189" s="3">
+        <v>60051</v>
+      </c>
+      <c r="E189" s="5">
+        <f>D189/B服!D228</f>
+        <v>0.438120599715463</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="190" spans="1:6">
-      <c r="A190" s="2"/>
-      <c r="F190" s="2"/>
+      <c r="A190" s="2">
+        <v>299</v>
+      </c>
+      <c r="B190" s="7">
+        <v>46064</v>
+      </c>
+      <c r="C190" s="7">
+        <v>46073</v>
+      </c>
+      <c r="D190" s="3">
+        <v>67034</v>
+      </c>
+      <c r="E190" s="5">
+        <f>D190/B服!D229</f>
+        <v>0.419455360048056</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="A191" s="2"/>
-      <c r="F191" s="2"/>
+      <c r="A191" s="2">
+        <v>301</v>
+      </c>
+      <c r="B191" s="7">
+        <v>46075</v>
+      </c>
+      <c r="C191" s="7">
+        <v>46084</v>
+      </c>
+      <c r="D191" s="3">
+        <v>52585</v>
+      </c>
+      <c r="E191" s="5">
+        <f>D191/B服!D230</f>
+        <v>0.364912597239475</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2"/>

--- a/backend/config/playernumber.xlsx
+++ b/backend/config/playernumber.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -1096,7 +1096,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G230"/>
+  <dimension ref="A1:G231"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -5899,6 +5899,29 @@
         <v>7</v>
       </c>
       <c r="G230" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7">
+      <c r="A231" s="2">
+        <v>302</v>
+      </c>
+      <c r="B231" s="7">
+        <v>46086</v>
+      </c>
+      <c r="C231" s="7">
+        <v>46095</v>
+      </c>
+      <c r="D231" s="8">
+        <v>117319</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F231" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G231" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -9933,8 +9956,25 @@
       </c>
     </row>
     <row r="192" spans="1:6">
-      <c r="A192" s="2"/>
-      <c r="F192" s="2"/>
+      <c r="A192" s="2">
+        <v>302</v>
+      </c>
+      <c r="B192" s="7">
+        <v>46086</v>
+      </c>
+      <c r="C192" s="7">
+        <v>46095</v>
+      </c>
+      <c r="D192" s="3">
+        <v>35635</v>
+      </c>
+      <c r="E192" s="5">
+        <f>D192/B服!D231</f>
+        <v>0.303744491514588</v>
+      </c>
+      <c r="F192" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2"/>

--- a/backend/config/playernumber.xlsx
+++ b/backend/config/playernumber.xlsx
@@ -11,7 +11,7 @@
     <sheet name="渠道" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">B服!$A$1:$F$230</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">B服!$A$1:$F$231</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -1096,7 +1096,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G231"/>
+  <dimension ref="A1:G232"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -5915,8 +5915,8 @@
       <c r="D231" s="8">
         <v>117319</v>
       </c>
-      <c r="E231" s="2" t="s">
-        <v>10</v>
+      <c r="E231" s="2">
+        <v>2</v>
       </c>
       <c r="F231" s="2" t="s">
         <v>8</v>
@@ -5925,9 +5925,32 @@
         <v>15</v>
       </c>
     </row>
+    <row r="232" spans="1:7">
+      <c r="A232" s="2">
+        <v>303</v>
+      </c>
+      <c r="B232" s="7">
+        <v>46097</v>
+      </c>
+      <c r="C232" s="7">
+        <v>46106</v>
+      </c>
+      <c r="D232" s="8">
+        <v>113776</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G232" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F230" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F231" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:G193">
@@ -9977,8 +10000,25 @@
       </c>
     </row>
     <row r="193" spans="1:6">
-      <c r="A193" s="2"/>
-      <c r="F193" s="2"/>
+      <c r="A193" s="2">
+        <v>303</v>
+      </c>
+      <c r="B193" s="7">
+        <v>46097</v>
+      </c>
+      <c r="C193" s="7">
+        <v>46106</v>
+      </c>
+      <c r="D193" s="3">
+        <v>34715</v>
+      </c>
+      <c r="E193" s="5">
+        <f>D193/B服!D232</f>
+        <v>0.305117072141752</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="194" spans="1:6">
       <c r="A194" s="2"/>

--- a/backend/config/playernumber.xlsx
+++ b/backend/config/playernumber.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="B服" sheetId="1" r:id="rId1"/>
     <sheet name="渠道" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">B服!$A$1:$F$231</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">B服!$A$1:$F$232</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -1096,7 +1096,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G232"/>
+  <dimension ref="A1:G233"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -5948,9 +5948,32 @@
         <v>15</v>
       </c>
     </row>
+    <row r="233" spans="1:7">
+      <c r="A233" s="2">
+        <v>304</v>
+      </c>
+      <c r="B233" s="7">
+        <v>46108</v>
+      </c>
+      <c r="C233" s="7">
+        <v>46117</v>
+      </c>
+      <c r="D233" s="8">
+        <v>117630</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F233" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G233" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F231" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F232" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:G193">
@@ -10021,8 +10044,25 @@
       </c>
     </row>
     <row r="194" spans="1:6">
-      <c r="A194" s="2"/>
-      <c r="F194" s="2"/>
+      <c r="A194" s="2">
+        <v>304</v>
+      </c>
+      <c r="B194" s="7">
+        <v>46108</v>
+      </c>
+      <c r="C194" s="7">
+        <v>46117</v>
+      </c>
+      <c r="D194" s="3">
+        <v>43763</v>
+      </c>
+      <c r="E194" s="5">
+        <f>D194/B服!D233</f>
+        <v>0.372039445719629</v>
+      </c>
+      <c r="F194" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" s="2"/>

--- a/backend/config/playernumber.xlsx
+++ b/backend/config/playernumber.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="B服" sheetId="1" r:id="rId1"/>
     <sheet name="渠道" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">B服!$A$1:$F$232</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">B服!$A$1:$F$233</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -1096,7 +1096,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G233"/>
+  <dimension ref="A1:G234"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -5971,9 +5971,32 @@
         <v>15</v>
       </c>
     </row>
+    <row r="234" spans="1:7">
+      <c r="A234" s="2">
+        <v>305</v>
+      </c>
+      <c r="B234" s="7">
+        <v>46119</v>
+      </c>
+      <c r="C234" s="7">
+        <v>46127</v>
+      </c>
+      <c r="D234" s="8">
+        <v>50357</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F234" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G234" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F232" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F233" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:G193">
@@ -10065,8 +10088,25 @@
       </c>
     </row>
     <row r="195" spans="1:6">
-      <c r="A195" s="2"/>
-      <c r="F195" s="2"/>
+      <c r="A195" s="2">
+        <v>305</v>
+      </c>
+      <c r="B195" s="7">
+        <v>46119</v>
+      </c>
+      <c r="C195" s="7">
+        <v>46127</v>
+      </c>
+      <c r="D195" s="3">
+        <v>8885</v>
+      </c>
+      <c r="E195" s="5">
+        <f>D195/B服!D234</f>
+        <v>0.176440216851679</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" s="2"/>

--- a/backend/config/playernumber.xlsx
+++ b/backend/config/playernumber.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="B服" sheetId="1" r:id="rId1"/>
     <sheet name="渠道" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">B服!$A$1:$F$233</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">B服!$A$1:$F$234</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -1096,7 +1096,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G234"/>
+  <dimension ref="A1:G235"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -5984,8 +5984,8 @@
       <c r="D234" s="8">
         <v>50357</v>
       </c>
-      <c r="E234" s="2" t="s">
-        <v>10</v>
+      <c r="E234" s="2">
+        <v>1</v>
       </c>
       <c r="F234" s="2" t="s">
         <v>12</v>
@@ -5994,9 +5994,32 @@
         <v>15</v>
       </c>
     </row>
+    <row r="235" spans="1:7">
+      <c r="A235" s="2">
+        <v>306</v>
+      </c>
+      <c r="B235" s="7">
+        <v>46129</v>
+      </c>
+      <c r="C235" s="7">
+        <v>46136</v>
+      </c>
+      <c r="D235" s="8">
+        <v>109808</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F235" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G235" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F233" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F234" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:G193">
@@ -10109,8 +10132,25 @@
       </c>
     </row>
     <row r="196" spans="1:6">
-      <c r="A196" s="2"/>
-      <c r="F196" s="2"/>
+      <c r="A196" s="2">
+        <v>306</v>
+      </c>
+      <c r="B196" s="7">
+        <v>46129</v>
+      </c>
+      <c r="C196" s="7">
+        <v>46136</v>
+      </c>
+      <c r="D196" s="3">
+        <v>37767</v>
+      </c>
+      <c r="E196" s="5">
+        <f>D196/B服!D235</f>
+        <v>0.34393668949439</v>
+      </c>
+      <c r="F196" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" s="2"/>

--- a/backend/config/playernumber.xlsx
+++ b/backend/config/playernumber.xlsx
@@ -11,7 +11,7 @@
     <sheet name="渠道" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">B服!$A$1:$F$234</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">B服!$A$1:$F$235</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -1096,7 +1096,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G235"/>
+  <dimension ref="A1:G236"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -6017,9 +6017,32 @@
         <v>15</v>
       </c>
     </row>
+    <row r="236" spans="1:7">
+      <c r="A236" s="2">
+        <v>307</v>
+      </c>
+      <c r="B236" s="7">
+        <v>46138</v>
+      </c>
+      <c r="C236" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D236" s="8">
+        <v>128828</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F236" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G236" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F234" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F235" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:G193">
@@ -10153,8 +10176,25 @@
       </c>
     </row>
     <row r="197" spans="1:6">
-      <c r="A197" s="2"/>
-      <c r="F197" s="2"/>
+      <c r="A197" s="2">
+        <v>307</v>
+      </c>
+      <c r="B197" s="7">
+        <v>46138</v>
+      </c>
+      <c r="C197" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D197" s="3">
+        <v>56030</v>
+      </c>
+      <c r="E197" s="5">
+        <f>D197/B服!D236</f>
+        <v>0.434920979911199</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="198" spans="1:6">
       <c r="A198" s="2"/>

--- a/backend/config/playernumber.xlsx
+++ b/backend/config/playernumber.xlsx
@@ -11,7 +11,7 @@
     <sheet name="渠道" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">B服!$A$1:$F$235</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">B服!$A$1:$F$236</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -1096,7 +1096,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G236"/>
+  <dimension ref="A1:G241"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -6040,9 +6040,73 @@
         <v>15</v>
       </c>
     </row>
+    <row r="237" spans="1:7">
+      <c r="A237" s="2">
+        <v>308</v>
+      </c>
+      <c r="B237" s="7">
+        <v>46148</v>
+      </c>
+      <c r="C237" s="7">
+        <v>46156</v>
+      </c>
+      <c r="D237" s="8">
+        <v>99911</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F237" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G237" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7">
+      <c r="A238" s="2">
+        <v>309</v>
+      </c>
+      <c r="F238" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G238" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7">
+      <c r="A239" s="2">
+        <v>311</v>
+      </c>
+      <c r="F239" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G239" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7">
+      <c r="A240" s="2">
+        <v>310</v>
+      </c>
+      <c r="F240" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G240" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
+      <c r="A241" s="2">
+        <v>314</v>
+      </c>
+      <c r="G241" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F235" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F236" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:G193">
@@ -10197,20 +10261,54 @@
       </c>
     </row>
     <row r="198" spans="1:6">
-      <c r="A198" s="2"/>
-      <c r="F198" s="2"/>
+      <c r="A198" s="2">
+        <v>308</v>
+      </c>
+      <c r="B198" s="7">
+        <v>46148</v>
+      </c>
+      <c r="C198" s="7">
+        <v>46156</v>
+      </c>
+      <c r="D198" s="3">
+        <v>31921</v>
+      </c>
+      <c r="E198" s="5">
+        <f>D198/B服!D237</f>
+        <v>0.319494349971475</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="199" spans="1:6">
-      <c r="A199" s="2"/>
+      <c r="A199" s="2">
+        <v>309</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="200" spans="1:6">
-      <c r="A200" s="2"/>
+      <c r="A200" s="2">
+        <v>311</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="201" spans="1:6">
-      <c r="A201" s="2"/>
+      <c r="A201" s="2">
+        <v>310</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="202" spans="1:6">
-      <c r="A202" s="2"/>
+      <c r="A202" s="2">
+        <v>314</v>
+      </c>
     </row>
     <row r="203" spans="1:6">
       <c r="A203" s="2"/>
@@ -10353,7 +10451,7 @@
     <sortCondition ref="A2:A134"/>
   </sortState>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F198">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F197 F198:F201">
       <formula1>"一般活动（协力）,挑战LIVE（CP）,竞演LIVE（对邦）,LIVE试炼（EX）,任务LIVE（协力）,团队LIVE FES （5V5）,组曲LIVE（3组曲）"</formula1>
     </dataValidation>
   </dataValidations>

--- a/backend/config/playernumber.xlsx
+++ b/backend/config/playernumber.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -6090,6 +6090,18 @@
       <c r="A239" s="2">
         <v>311</v>
       </c>
+      <c r="B239" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C239" s="8">
+        <v>46176</v>
+      </c>
+      <c r="D239" s="4">
+        <v>155478</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="F239" s="2" t="s">
         <v>6</v>
       </c>
@@ -10905,7 +10917,9 @@
         <f>D199/B服!D238</f>
         <v>0.431696914381999</v>
       </c>
-      <c r="F199" s="2"/>
+      <c r="F199" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="G199" s="2" t="s">
         <v>7</v>
       </c>
@@ -10914,7 +10928,22 @@
       <c r="A200" s="2">
         <v>311</v>
       </c>
-      <c r="F200" s="2"/>
+      <c r="B200" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C200" s="8">
+        <v>46176</v>
+      </c>
+      <c r="D200" s="3">
+        <v>47728</v>
+      </c>
+      <c r="E200" s="6">
+        <f>D200/B服!D239</f>
+        <v>0.306975906559127</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="G200" s="2" t="s">
         <v>6</v>
       </c>

--- a/backend/config/playernumber.xlsx
+++ b/backend/config/playernumber.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -6113,6 +6113,18 @@
       <c r="A240" s="2">
         <v>310</v>
       </c>
+      <c r="B240" s="8">
+        <v>46178</v>
+      </c>
+      <c r="C240" s="8">
+        <v>46186</v>
+      </c>
+      <c r="D240" s="4">
+        <v>150493</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="F240" s="2" t="s">
         <v>11</v>
       </c>
@@ -10952,7 +10964,22 @@
       <c r="A201" s="2">
         <v>310</v>
       </c>
-      <c r="F201" s="2"/>
+      <c r="B201" s="8">
+        <v>46178</v>
+      </c>
+      <c r="C201" s="8">
+        <v>46186</v>
+      </c>
+      <c r="D201" s="3">
+        <v>49441</v>
+      </c>
+      <c r="E201" s="6">
+        <f>D201/B服!D240</f>
+        <v>0.32852690822829</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="G201" s="2" t="s">
         <v>11</v>
       </c>

--- a/backend/config/playernumber.xlsx
+++ b/backend/config/playernumber.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -6136,6 +6136,21 @@
       <c r="A241" s="2">
         <v>314</v>
       </c>
+      <c r="B241" s="8">
+        <v>46188</v>
+      </c>
+      <c r="C241" s="8">
+        <v>46196</v>
+      </c>
+      <c r="D241" s="4">
+        <v>145866</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F241" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="G241" s="4" t="s">
         <v>15</v>
       </c>
@@ -6162,7 +6177,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G247"/>
+  <dimension ref="A1:G264"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -10988,177 +11003,291 @@
       <c r="A202" s="2">
         <v>314</v>
       </c>
-      <c r="F202" s="2"/>
+      <c r="B202" s="8">
+        <v>46188</v>
+      </c>
+      <c r="C202" s="8">
+        <v>46196</v>
+      </c>
+      <c r="D202" s="3">
+        <v>50176</v>
+      </c>
+      <c r="E202" s="6">
+        <f>D202/B服!D241</f>
+        <v>0.343986946923889</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G202" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="203" spans="1:7">
       <c r="A203" s="2"/>
       <c r="F203" s="2"/>
+      <c r="G203" s="2"/>
     </row>
     <row r="204" spans="1:7">
       <c r="A204" s="2"/>
       <c r="F204" s="2"/>
+      <c r="G204" s="2"/>
     </row>
     <row r="205" spans="1:7">
       <c r="A205" s="2"/>
       <c r="F205" s="2"/>
+      <c r="G205" s="2"/>
     </row>
     <row r="206" spans="1:7">
       <c r="A206" s="2"/>
       <c r="F206" s="2"/>
+      <c r="G206" s="2"/>
     </row>
     <row r="207" spans="1:7">
       <c r="A207" s="2"/>
       <c r="F207" s="2"/>
+      <c r="G207" s="2"/>
     </row>
     <row r="208" spans="1:7">
       <c r="A208" s="2"/>
       <c r="F208" s="2"/>
-    </row>
-    <row r="209" spans="1:6">
+      <c r="G208" s="2"/>
+    </row>
+    <row r="209" spans="1:7">
       <c r="A209" s="2"/>
       <c r="F209" s="2"/>
-    </row>
-    <row r="210" spans="1:6">
+      <c r="G209" s="2"/>
+    </row>
+    <row r="210" spans="1:7">
       <c r="A210" s="2"/>
       <c r="F210" s="2"/>
-    </row>
-    <row r="211" spans="1:6">
+      <c r="G210" s="2"/>
+    </row>
+    <row r="211" spans="1:7">
       <c r="A211" s="2"/>
       <c r="F211" s="2"/>
-    </row>
-    <row r="212" spans="1:6">
+      <c r="G211" s="2"/>
+    </row>
+    <row r="212" spans="1:7">
       <c r="A212" s="2"/>
       <c r="F212" s="2"/>
-    </row>
-    <row r="213" spans="1:6">
+      <c r="G212" s="2"/>
+    </row>
+    <row r="213" spans="1:7">
       <c r="A213" s="2"/>
       <c r="F213" s="2"/>
-    </row>
-    <row r="214" spans="1:6">
+      <c r="G213" s="2"/>
+    </row>
+    <row r="214" spans="1:7">
       <c r="A214" s="2"/>
       <c r="F214" s="2"/>
-    </row>
-    <row r="215" spans="1:6">
+      <c r="G214" s="2"/>
+    </row>
+    <row r="215" spans="1:7">
       <c r="A215" s="2"/>
       <c r="F215" s="2"/>
-    </row>
-    <row r="216" spans="1:6">
+      <c r="G215" s="2"/>
+    </row>
+    <row r="216" spans="1:7">
       <c r="A216" s="2"/>
       <c r="F216" s="2"/>
-    </row>
-    <row r="217" spans="1:6">
+      <c r="G216" s="2"/>
+    </row>
+    <row r="217" spans="1:7">
       <c r="A217" s="2"/>
       <c r="F217" s="2"/>
-    </row>
-    <row r="218" spans="1:6">
+      <c r="G217" s="2"/>
+    </row>
+    <row r="218" spans="1:7">
       <c r="A218" s="2"/>
       <c r="F218" s="2"/>
-    </row>
-    <row r="219" spans="1:6">
+      <c r="G218" s="2"/>
+    </row>
+    <row r="219" spans="1:7">
       <c r="A219" s="2"/>
       <c r="F219" s="2"/>
-    </row>
-    <row r="220" spans="1:6">
+      <c r="G219" s="2"/>
+    </row>
+    <row r="220" spans="1:7">
       <c r="A220" s="2"/>
       <c r="F220" s="2"/>
-    </row>
-    <row r="221" spans="1:6">
+      <c r="G220" s="2"/>
+    </row>
+    <row r="221" spans="1:7">
       <c r="A221" s="2"/>
       <c r="F221" s="2"/>
-    </row>
-    <row r="222" spans="1:6">
+      <c r="G221" s="2"/>
+    </row>
+    <row r="222" spans="1:7">
       <c r="A222" s="2"/>
       <c r="F222" s="2"/>
-    </row>
-    <row r="223" spans="1:6">
+      <c r="G222" s="2"/>
+    </row>
+    <row r="223" spans="1:7">
       <c r="A223" s="2"/>
       <c r="F223" s="2"/>
-    </row>
-    <row r="224" spans="1:6">
+      <c r="G223" s="2"/>
+    </row>
+    <row r="224" spans="1:7">
       <c r="A224" s="2"/>
       <c r="F224" s="2"/>
-    </row>
-    <row r="225" spans="1:6">
+      <c r="G224" s="2"/>
+    </row>
+    <row r="225" spans="1:7">
       <c r="A225" s="2"/>
       <c r="F225" s="2"/>
-    </row>
-    <row r="226" spans="1:6">
+      <c r="G225" s="2"/>
+    </row>
+    <row r="226" spans="1:7">
       <c r="A226" s="2"/>
       <c r="F226" s="2"/>
-    </row>
-    <row r="227" spans="1:6">
+      <c r="G226" s="2"/>
+    </row>
+    <row r="227" spans="1:7">
       <c r="A227" s="2"/>
       <c r="F227" s="2"/>
-    </row>
-    <row r="228" spans="1:6">
+      <c r="G227" s="2"/>
+    </row>
+    <row r="228" spans="1:7">
       <c r="A228" s="2"/>
       <c r="F228" s="2"/>
-    </row>
-    <row r="229" spans="1:6">
+      <c r="G228" s="2"/>
+    </row>
+    <row r="229" spans="1:7">
       <c r="A229" s="2"/>
       <c r="F229" s="2"/>
-    </row>
-    <row r="230" spans="1:6">
+      <c r="G229" s="2"/>
+    </row>
+    <row r="230" spans="1:7">
       <c r="A230" s="2"/>
       <c r="F230" s="2"/>
-    </row>
-    <row r="231" spans="1:6">
+      <c r="G230" s="2"/>
+    </row>
+    <row r="231" spans="1:7">
       <c r="A231" s="2"/>
       <c r="F231" s="2"/>
-    </row>
-    <row r="232" spans="1:6">
+      <c r="G231" s="2"/>
+    </row>
+    <row r="232" spans="1:7">
       <c r="A232" s="2"/>
       <c r="F232" s="2"/>
-    </row>
-    <row r="233" spans="1:6">
+      <c r="G232" s="2"/>
+    </row>
+    <row r="233" spans="1:7">
       <c r="A233" s="2"/>
       <c r="F233" s="2"/>
-    </row>
-    <row r="234" spans="1:6">
+      <c r="G233" s="2"/>
+    </row>
+    <row r="234" spans="1:7">
       <c r="A234" s="2"/>
       <c r="F234" s="2"/>
-    </row>
-    <row r="235" spans="1:6">
+      <c r="G234" s="2"/>
+    </row>
+    <row r="235" spans="1:7">
       <c r="A235" s="2"/>
       <c r="F235" s="2"/>
-    </row>
-    <row r="236" spans="1:6">
+      <c r="G235" s="2"/>
+    </row>
+    <row r="236" spans="1:7">
       <c r="A236" s="2"/>
       <c r="F236" s="2"/>
-    </row>
-    <row r="237" spans="1:6">
+      <c r="G236" s="2"/>
+    </row>
+    <row r="237" spans="1:7">
       <c r="A237" s="2"/>
       <c r="F237" s="2"/>
-    </row>
-    <row r="238" spans="1:6">
+      <c r="G237" s="2"/>
+    </row>
+    <row r="238" spans="1:7">
       <c r="A238" s="2"/>
-    </row>
-    <row r="239" spans="1:6">
+      <c r="G238" s="2"/>
+    </row>
+    <row r="239" spans="1:7">
       <c r="A239" s="2"/>
-    </row>
-    <row r="240" spans="1:6">
+      <c r="G239" s="2"/>
+    </row>
+    <row r="240" spans="1:7">
       <c r="A240" s="2"/>
-    </row>
-    <row r="241" spans="1:1">
+      <c r="G240" s="2"/>
+    </row>
+    <row r="241" spans="1:7">
       <c r="A241" s="2"/>
-    </row>
-    <row r="242" spans="1:1">
+      <c r="G241" s="2"/>
+    </row>
+    <row r="242" spans="1:7">
       <c r="A242" s="2"/>
-    </row>
-    <row r="243" spans="1:1">
+      <c r="G242" s="2"/>
+    </row>
+    <row r="243" spans="1:7">
       <c r="A243" s="2"/>
-    </row>
-    <row r="244" spans="1:1">
+      <c r="G243" s="2"/>
+    </row>
+    <row r="244" spans="1:7">
       <c r="A244" s="2"/>
-    </row>
-    <row r="245" spans="1:1">
+      <c r="G244" s="2"/>
+    </row>
+    <row r="245" spans="1:7">
       <c r="A245" s="2"/>
-    </row>
-    <row r="246" spans="1:1">
+      <c r="G245" s="2"/>
+    </row>
+    <row r="246" spans="1:7">
       <c r="A246" s="2"/>
-    </row>
-    <row r="247" spans="1:1">
+      <c r="G246" s="2"/>
+    </row>
+    <row r="247" spans="1:7">
       <c r="A247" s="2"/>
+      <c r="G247" s="2"/>
+    </row>
+    <row r="248" spans="1:7">
+      <c r="G248" s="2"/>
+    </row>
+    <row r="249" spans="1:7">
+      <c r="G249" s="2"/>
+    </row>
+    <row r="250" spans="1:7">
+      <c r="G250" s="2"/>
+    </row>
+    <row r="251" spans="1:7">
+      <c r="G251" s="2"/>
+    </row>
+    <row r="252" spans="1:7">
+      <c r="G252" s="2"/>
+    </row>
+    <row r="253" spans="1:7">
+      <c r="G253" s="2"/>
+    </row>
+    <row r="254" spans="1:7">
+      <c r="G254" s="2"/>
+    </row>
+    <row r="255" spans="1:7">
+      <c r="G255" s="2"/>
+    </row>
+    <row r="256" spans="1:7">
+      <c r="G256" s="2"/>
+    </row>
+    <row r="257" spans="7:7">
+      <c r="G257" s="2"/>
+    </row>
+    <row r="258" spans="7:7">
+      <c r="G258" s="2"/>
+    </row>
+    <row r="259" spans="7:7">
+      <c r="G259" s="2"/>
+    </row>
+    <row r="260" spans="7:7">
+      <c r="G260" s="2"/>
+    </row>
+    <row r="261" spans="7:7">
+      <c r="G261" s="2"/>
+    </row>
+    <row r="262" spans="7:7">
+      <c r="G262" s="2"/>
+    </row>
+    <row r="263" spans="7:7">
+      <c r="G263" s="2"/>
+    </row>
+    <row r="264" spans="7:7">
+      <c r="G264" s="2"/>
     </row>
   </sheetData>
   <sortState ref="A2:G134">
@@ -11166,7 +11295,7 @@
     <sortCondition ref="A2:A134"/>
   </sortState>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G201">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G201 G2:G200 G202:G264">
       <formula1>"一般活动（协力）,挑战LIVE（CP）,竞演LIVE（对邦）,LIVE试炼（EX）,任务LIVE（协力）,团队LIVE FES （5V5）,组曲LIVE（3组曲）"</formula1>
     </dataValidation>
   </dataValidations>

--- a/backend/config/playernumber.xlsx
+++ b/backend/config/playernumber.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -1096,7 +1096,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G241"/>
+  <dimension ref="A1:G262"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -6145,14 +6145,137 @@
       <c r="D241" s="4">
         <v>145866</v>
       </c>
-      <c r="E241" s="2" t="s">
-        <v>10</v>
+      <c r="E241" s="2">
+        <v>3</v>
       </c>
       <c r="F241" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G241" s="4" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7">
+      <c r="A242" s="2">
+        <v>315</v>
+      </c>
+      <c r="B242" s="8">
+        <v>46198</v>
+      </c>
+      <c r="C242" s="8">
+        <v>46207</v>
+      </c>
+      <c r="D242" s="4">
+        <v>136867</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F242" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G242" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7">
+      <c r="A243" s="2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7">
+      <c r="A244" s="2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7">
+      <c r="A245" s="2">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7">
+      <c r="A246" s="2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7">
+      <c r="A247" s="2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7">
+      <c r="A248" s="2">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7">
+      <c r="A249" s="2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7">
+      <c r="A250" s="2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7">
+      <c r="A251" s="2">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7">
+      <c r="A252" s="2">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7">
+      <c r="A253" s="2">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7">
+      <c r="A254" s="2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7">
+      <c r="A255" s="2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7">
+      <c r="A256" s="2">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257" s="2">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258" s="2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259" s="2">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260" s="2">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261" s="2">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262" s="2">
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -11024,107 +11147,166 @@
       </c>
     </row>
     <row r="203" spans="1:7">
-      <c r="A203" s="2"/>
-      <c r="F203" s="2"/>
-      <c r="G203" s="2"/>
+      <c r="A203" s="2">
+        <v>315</v>
+      </c>
+      <c r="B203" s="8">
+        <v>46198</v>
+      </c>
+      <c r="C203" s="8">
+        <v>46207</v>
+      </c>
+      <c r="D203" s="3">
+        <v>64014</v>
+      </c>
+      <c r="E203" s="6">
+        <f>D203/B服!D242</f>
+        <v>0.467709528228134</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G203" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="204" spans="1:7">
-      <c r="A204" s="2"/>
+      <c r="A204" s="2">
+        <v>316</v>
+      </c>
       <c r="F204" s="2"/>
       <c r="G204" s="2"/>
     </row>
     <row r="205" spans="1:7">
-      <c r="A205" s="2"/>
+      <c r="A205" s="2">
+        <v>317</v>
+      </c>
       <c r="F205" s="2"/>
       <c r="G205" s="2"/>
     </row>
     <row r="206" spans="1:7">
-      <c r="A206" s="2"/>
+      <c r="A206" s="2">
+        <v>318</v>
+      </c>
       <c r="F206" s="2"/>
       <c r="G206" s="2"/>
     </row>
     <row r="207" spans="1:7">
-      <c r="A207" s="2"/>
+      <c r="A207" s="2">
+        <v>319</v>
+      </c>
       <c r="F207" s="2"/>
       <c r="G207" s="2"/>
     </row>
     <row r="208" spans="1:7">
-      <c r="A208" s="2"/>
+      <c r="A208" s="2">
+        <v>320</v>
+      </c>
       <c r="F208" s="2"/>
       <c r="G208" s="2"/>
     </row>
     <row r="209" spans="1:7">
-      <c r="A209" s="2"/>
+      <c r="A209" s="2">
+        <v>321</v>
+      </c>
       <c r="F209" s="2"/>
       <c r="G209" s="2"/>
     </row>
     <row r="210" spans="1:7">
-      <c r="A210" s="2"/>
+      <c r="A210" s="2">
+        <v>322</v>
+      </c>
       <c r="F210" s="2"/>
       <c r="G210" s="2"/>
     </row>
     <row r="211" spans="1:7">
-      <c r="A211" s="2"/>
+      <c r="A211" s="2">
+        <v>323</v>
+      </c>
       <c r="F211" s="2"/>
       <c r="G211" s="2"/>
     </row>
     <row r="212" spans="1:7">
-      <c r="A212" s="2"/>
+      <c r="A212" s="2">
+        <v>324</v>
+      </c>
       <c r="F212" s="2"/>
       <c r="G212" s="2"/>
     </row>
     <row r="213" spans="1:7">
-      <c r="A213" s="2"/>
+      <c r="A213" s="2">
+        <v>325</v>
+      </c>
       <c r="F213" s="2"/>
       <c r="G213" s="2"/>
     </row>
     <row r="214" spans="1:7">
-      <c r="A214" s="2"/>
+      <c r="A214" s="2">
+        <v>326</v>
+      </c>
       <c r="F214" s="2"/>
       <c r="G214" s="2"/>
     </row>
     <row r="215" spans="1:7">
-      <c r="A215" s="2"/>
+      <c r="A215" s="2">
+        <v>327</v>
+      </c>
       <c r="F215" s="2"/>
       <c r="G215" s="2"/>
     </row>
     <row r="216" spans="1:7">
-      <c r="A216" s="2"/>
+      <c r="A216" s="2">
+        <v>328</v>
+      </c>
       <c r="F216" s="2"/>
       <c r="G216" s="2"/>
     </row>
     <row r="217" spans="1:7">
-      <c r="A217" s="2"/>
+      <c r="A217" s="2">
+        <v>329</v>
+      </c>
       <c r="F217" s="2"/>
       <c r="G217" s="2"/>
     </row>
     <row r="218" spans="1:7">
-      <c r="A218" s="2"/>
+      <c r="A218" s="2">
+        <v>330</v>
+      </c>
       <c r="F218" s="2"/>
       <c r="G218" s="2"/>
     </row>
     <row r="219" spans="1:7">
-      <c r="A219" s="2"/>
+      <c r="A219" s="2">
+        <v>331</v>
+      </c>
       <c r="F219" s="2"/>
       <c r="G219" s="2"/>
     </row>
     <row r="220" spans="1:7">
-      <c r="A220" s="2"/>
+      <c r="A220" s="2">
+        <v>332</v>
+      </c>
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
     </row>
     <row r="221" spans="1:7">
-      <c r="A221" s="2"/>
+      <c r="A221" s="2">
+        <v>333</v>
+      </c>
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
     </row>
     <row r="222" spans="1:7">
-      <c r="A222" s="2"/>
+      <c r="A222" s="2">
+        <v>334</v>
+      </c>
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
     </row>
     <row r="223" spans="1:7">
-      <c r="A223" s="2"/>
+      <c r="A223" s="2">
+        <v>335</v>
+      </c>
       <c r="F223" s="2"/>
       <c r="G223" s="2"/>
     </row>
@@ -11295,7 +11477,7 @@
     <sortCondition ref="A2:A134"/>
   </sortState>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G201 G2:G200 G202:G264">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G264">
       <formula1>"一般活动（协力）,挑战LIVE（CP）,竞演LIVE（对邦）,LIVE试炼（EX）,任务LIVE（协力）,团队LIVE FES （5V5）,组曲LIVE（3组曲）"</formula1>
     </dataValidation>
   </dataValidations>

--- a/backend/config/playernumber.xlsx
+++ b/backend/config/playernumber.xlsx
@@ -11,7 +11,7 @@
     <sheet name="渠道" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">B服!$A$1:$F$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">B服!$A$1:$F$262</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -6182,6 +6182,24 @@
       <c r="A243" s="2">
         <v>316</v>
       </c>
+      <c r="B243" s="8">
+        <v>46209</v>
+      </c>
+      <c r="C243" s="8">
+        <v>46217</v>
+      </c>
+      <c r="D243" s="4">
+        <v>138703</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F243" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G243" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="244" spans="1:7">
       <c r="A244" s="2">
@@ -6280,7 +6298,7 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F241" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F262" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:G193">
@@ -11174,8 +11192,25 @@
       <c r="A204" s="2">
         <v>316</v>
       </c>
-      <c r="F204" s="2"/>
-      <c r="G204" s="2"/>
+      <c r="B204" s="8">
+        <v>46209</v>
+      </c>
+      <c r="C204" s="8">
+        <v>46217</v>
+      </c>
+      <c r="D204" s="3">
+        <v>65267</v>
+      </c>
+      <c r="E204" s="6">
+        <f>D204/B服!D243</f>
+        <v>0.470552187047144</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G204" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="205" spans="1:7">
       <c r="A205" s="2">
